--- a/Источники/файлы данных/Gr_prog.xlsx
+++ b/Источники/файлы данных/Gr_prog.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gr_pr" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -576,7 +576,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -586,7 +586,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГХТхнУ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Сев(Аркт)ФУ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГВМетИ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КубГТхнУ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БелГТхнУ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтФУ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГВМетИ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтФУ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГТУ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтФУ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КрГТУ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВолгГУ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГГУ</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ЮЗГУ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГВМетИ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БрянГИТА</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГГУ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ЛипГТУ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГТУ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БрянГТУ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БрянГТУ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтГТУ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КубГТхнУ</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КрГАСА</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КнАГТУ</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтФУ</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГУПищП</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БашГУ</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КострГТУ</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ГУЦМиЗ</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ЮЗГУ</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВГТУ</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БрянГИТА</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КузГТУ</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КузГТУ</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГВМетИ</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГГУ</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГУ</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтФУ</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КрГТУ</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВолгГТУ</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВГТУ</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДагГУ</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтГТУ</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтГТУ</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГУ</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВологГТУ</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КоврГТА</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8812,7 +8812,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="B134" t="n">
         <v>7</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГГУ</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГГУ</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВятГУ</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГЭУ</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГЭУ</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДагГТУ</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДагГТУ</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГЭУ</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГУНГ</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВолгГУ</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГЭУ</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВГТУ</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КургГУ</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БайГУЭП</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГХТхнУ</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КубГУ</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВологГТУ</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МарГУ</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАМИ</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГХТхнУ</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВГТУ</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИжГТУ</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КургГУ</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГУП</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КБГУ</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтГТУ</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГУ</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГТУ</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КубГУ</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтГТУ</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ЛипГТУ</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БашГУ</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВятГУ</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БашГУ</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БайГУЭП</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВолгГУ</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БрянГТУ</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазГАСУ</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Сев(Аркт)ФУ</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КургГУ</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -16070,7 +16070,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КузГТУ</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВГТУ</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БрянГТУ</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГВМетИ</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГЭУ</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВятГУ</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КалмГУ</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГГУ</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтФУ</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГТУ</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БелГТхнУ</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ЮЗГУ</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БратГУ</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -18358,7 +18358,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КострГТУ</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -18486,7 +18486,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БратГУ</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -18550,7 +18550,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КубГТхнУ</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИндУ</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГУПБио</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГВМетИ</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДагГУ</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИндУ</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГЛТА</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -19498,7 +19498,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВСГУТиУ</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтГТУ</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ПовГТУ</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВГТУ</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -20010,7 +20010,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МагнГТУ</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КузГТУ</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БашГУ</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИвГАСУ</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -20330,7 +20330,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ПовГТУ</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГТУ</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -20778,7 +20778,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГУПищП</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -21150,7 +21150,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Сев(Аркт)ФУ</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -21202,7 +21202,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КургГУ</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КрГТУ</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -21394,7 +21394,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -21458,7 +21458,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СибФУ</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>СКГГТхнА</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ГУЦМиЗ</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КузГТУ</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -21906,7 +21906,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГЛТА</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУИТ</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИжГТУ</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГГУ</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АмурГУ</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КузГТУ</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -22610,7 +22610,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГУ</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -22738,7 +22738,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИЭМ</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -22802,7 +22802,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -22930,7 +22930,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -22994,7 +22994,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГУНГ</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГГУ</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -23378,7 +23378,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -23442,7 +23442,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -23506,7 +23506,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -23762,7 +23762,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВолгГТУ</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГТУ</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -23890,7 +23890,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ЛипГТУ</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВятГУ</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -24010,7 +24010,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ИркГУ</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -24074,7 +24074,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДонГТУ</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -24138,7 +24138,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БрянГТУ</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -24202,7 +24202,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГИндУ</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ЮЗГУ</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ДВГТУ</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -24518,7 +24518,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ГУЦМиЗ</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -24710,7 +24710,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГТекстУ</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -24838,7 +24838,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -24902,7 +24902,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -25030,7 +25030,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -25094,7 +25094,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>РГГРУ</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -25158,7 +25158,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>АлтГТУ</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАИ</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -25286,7 +25286,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВладГУ</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВолгГАСУ</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Каз(Прив)ФУ</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МАТИ</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -25594,7 +25594,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ВорГУ</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -25658,7 +25658,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>КазНИТУ-КАИ</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>МГТекстУ</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -25786,7 +25786,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>БалтГТУ</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">

--- a/Источники/файлы данных/Gr_prog.xlsx
+++ b/Источники/файлы данных/Gr_prog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,12 +431,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>codkon</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>codproj</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>codkon</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -512,10 +512,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
         <v>2</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>53</v>
@@ -576,10 +576,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>121</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>44</v>
@@ -640,10 +640,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
         <v>4</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
         <v>5</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>93</v>
@@ -768,10 +768,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
         <v>6</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>93</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
         <v>7</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>90</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
         <v>15</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -960,10 +960,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
         <v>16</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>92</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
         <v>17</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>93</v>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
         <v>23</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>96</v>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
         <v>24</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>92</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
         <v>27</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>70</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
         <v>37</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>53</v>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
         <v>41</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>53</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
         <v>49</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>92</v>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
         <v>50</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>93</v>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
         <v>51</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
         <v>52</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>60</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
         <v>53</v>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>13</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
         <v>61</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>92</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
         <v>63</v>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>55</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
         <v>64</v>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>93</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
         <v>68</v>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>90</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
         <v>73</v>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>71</v>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
         <v>75</v>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>92</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
         <v>76</v>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>96</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
         <v>77</v>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>80</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
         <v>78</v>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>80</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
         <v>81</v>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>90</v>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
         <v>84</v>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>60</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
         <v>87</v>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>51</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
         <v>89</v>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>18</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
         <v>90</v>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>2</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
         <v>91</v>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
       </c>
       <c r="C35" t="n">
         <v>21</v>
@@ -2680,10 +2680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
         <v>94</v>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>38</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
         <v>97</v>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
       </c>
       <c r="C37" t="n">
         <v>38</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="n">
         <v>100</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>60</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="n">
         <v>102</v>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
       </c>
       <c r="C39" t="n">
         <v>74</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="n">
         <v>107</v>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>71</v>
@@ -3000,10 +3000,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="n">
         <v>109</v>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>13</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
         <v>112</v>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
       </c>
       <c r="C42" t="n">
         <v>92</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="n">
         <v>115</v>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
       </c>
       <c r="C43" t="n">
         <v>100</v>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="n">
         <v>116</v>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
       </c>
       <c r="C44" t="n">
         <v>92</v>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="n">
         <v>118</v>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
       </c>
       <c r="C45" t="n">
         <v>13</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="n">
         <v>120</v>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
       </c>
       <c r="C46" t="n">
         <v>14</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" t="n">
         <v>1</v>
-      </c>
-      <c r="B47" t="n">
-        <v>2</v>
       </c>
       <c r="C47" t="n">
         <v>90</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" t="n">
         <v>9</v>
-      </c>
-      <c r="B48" t="n">
-        <v>2</v>
       </c>
       <c r="C48" t="n">
         <v>53</v>
@@ -3512,10 +3512,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="n">
         <v>10</v>
-      </c>
-      <c r="B49" t="n">
-        <v>2</v>
       </c>
       <c r="C49" t="n">
         <v>92</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" t="n">
         <v>16</v>
-      </c>
-      <c r="B50" t="n">
-        <v>2</v>
       </c>
       <c r="C50" t="n">
         <v>97</v>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="n">
         <v>23</v>
-      </c>
-      <c r="B51" t="n">
-        <v>2</v>
       </c>
       <c r="C51" t="n">
         <v>90</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" t="n">
         <v>25</v>
-      </c>
-      <c r="B52" t="n">
-        <v>2</v>
       </c>
       <c r="C52" t="n">
         <v>78</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" t="n">
         <v>37</v>
-      </c>
-      <c r="B53" t="n">
-        <v>2</v>
       </c>
       <c r="C53" t="n">
         <v>93</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="n">
         <v>45</v>
-      </c>
-      <c r="B54" t="n">
-        <v>2</v>
       </c>
       <c r="C54" t="n">
         <v>71</v>
@@ -3888,10 +3888,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" t="n">
         <v>46</v>
-      </c>
-      <c r="B55" t="n">
-        <v>2</v>
       </c>
       <c r="C55" t="n">
         <v>71</v>
@@ -3952,10 +3952,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="n">
         <v>48</v>
-      </c>
-      <c r="B56" t="n">
-        <v>2</v>
       </c>
       <c r="C56" t="n">
         <v>96</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" t="n">
         <v>61</v>
-      </c>
-      <c r="B57" t="n">
-        <v>2</v>
       </c>
       <c r="C57" t="n">
         <v>12</v>
@@ -4076,10 +4076,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" t="n">
         <v>69</v>
-      </c>
-      <c r="B58" t="n">
-        <v>2</v>
       </c>
       <c r="C58" t="n">
         <v>93</v>
@@ -4132,10 +4132,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" t="n">
         <v>72</v>
-      </c>
-      <c r="B59" t="n">
-        <v>2</v>
       </c>
       <c r="C59" t="n">
         <v>97</v>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" t="n">
         <v>75</v>
-      </c>
-      <c r="B60" t="n">
-        <v>2</v>
       </c>
       <c r="C60" t="n">
         <v>79</v>
@@ -4252,10 +4252,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" t="n">
         <v>77</v>
-      </c>
-      <c r="B61" t="n">
-        <v>2</v>
       </c>
       <c r="C61" t="n">
         <v>21</v>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
+        <v>2</v>
+      </c>
+      <c r="B62" t="n">
         <v>80</v>
-      </c>
-      <c r="B62" t="n">
-        <v>2</v>
       </c>
       <c r="C62" t="n">
         <v>18</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" t="n">
         <v>87</v>
-      </c>
-      <c r="B63" t="n">
-        <v>2</v>
       </c>
       <c r="C63" t="n">
         <v>13</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
+        <v>2</v>
+      </c>
+      <c r="B64" t="n">
         <v>89</v>
-      </c>
-      <c r="B64" t="n">
-        <v>2</v>
       </c>
       <c r="C64" t="n">
         <v>11</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
+        <v>2</v>
+      </c>
+      <c r="B65" t="n">
         <v>92</v>
-      </c>
-      <c r="B65" t="n">
-        <v>2</v>
       </c>
       <c r="C65" t="n">
         <v>11</v>
@@ -4548,10 +4548,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
+        <v>2</v>
+      </c>
+      <c r="B66" t="n">
         <v>93</v>
-      </c>
-      <c r="B66" t="n">
-        <v>2</v>
       </c>
       <c r="C66" t="n">
         <v>93</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" t="n">
         <v>5</v>
-      </c>
-      <c r="B68" t="n">
-        <v>3</v>
       </c>
       <c r="C68" t="n">
         <v>13</v>
@@ -4736,10 +4736,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" t="n">
         <v>10</v>
-      </c>
-      <c r="B69" t="n">
-        <v>3</v>
       </c>
       <c r="C69" t="n">
         <v>93</v>
@@ -4796,10 +4796,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" t="n">
         <v>11</v>
-      </c>
-      <c r="B70" t="n">
-        <v>3</v>
       </c>
       <c r="C70" t="n">
         <v>38</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" t="n">
         <v>13</v>
-      </c>
-      <c r="B71" t="n">
-        <v>3</v>
       </c>
       <c r="C71" t="n">
         <v>51</v>
@@ -4924,10 +4924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" t="n">
         <v>14</v>
-      </c>
-      <c r="B72" t="n">
-        <v>3</v>
       </c>
       <c r="C72" t="n">
         <v>70</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
+        <v>3</v>
+      </c>
+      <c r="B73" t="n">
         <v>15</v>
-      </c>
-      <c r="B73" t="n">
-        <v>3</v>
       </c>
       <c r="C73" t="n">
         <v>36</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" t="n">
         <v>16</v>
-      </c>
-      <c r="B74" t="n">
-        <v>3</v>
       </c>
       <c r="C74" t="n">
         <v>38</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" t="n">
         <v>26</v>
-      </c>
-      <c r="B75" t="n">
-        <v>3</v>
       </c>
       <c r="C75" t="n">
         <v>51</v>
@@ -5180,10 +5180,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
+        <v>3</v>
+      </c>
+      <c r="B76" t="n">
         <v>28</v>
-      </c>
-      <c r="B76" t="n">
-        <v>3</v>
       </c>
       <c r="C76" t="n">
         <v>72</v>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" t="n">
         <v>19</v>
-      </c>
-      <c r="B77" t="n">
-        <v>4</v>
       </c>
       <c r="C77" t="n">
         <v>68</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" t="n">
         <v>23</v>
-      </c>
-      <c r="B78" t="n">
-        <v>4</v>
       </c>
       <c r="C78" t="n">
         <v>55</v>
@@ -5348,10 +5348,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="n">
         <v>24</v>
-      </c>
-      <c r="B79" t="n">
-        <v>4</v>
       </c>
       <c r="C79" t="n">
         <v>60</v>
@@ -5400,10 +5400,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" t="n">
         <v>31</v>
-      </c>
-      <c r="B80" t="n">
-        <v>4</v>
       </c>
       <c r="C80" t="n">
         <v>88</v>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" t="n">
         <v>32</v>
-      </c>
-      <c r="B81" t="n">
-        <v>4</v>
       </c>
       <c r="C81" t="n">
         <v>57</v>
@@ -5504,10 +5504,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" t="n">
         <v>33</v>
-      </c>
-      <c r="B82" t="n">
-        <v>4</v>
       </c>
       <c r="C82" t="n">
         <v>7</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
+        <v>4</v>
+      </c>
+      <c r="B83" t="n">
         <v>43</v>
-      </c>
-      <c r="B83" t="n">
-        <v>4</v>
       </c>
       <c r="C83" t="n">
         <v>18</v>
@@ -5620,10 +5620,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
+        <v>4</v>
+      </c>
+      <c r="B84" t="n">
         <v>49</v>
-      </c>
-      <c r="B84" t="n">
-        <v>4</v>
       </c>
       <c r="C84" t="n">
         <v>71</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" t="n">
         <v>50</v>
-      </c>
-      <c r="B85" t="n">
-        <v>4</v>
       </c>
       <c r="C85" t="n">
         <v>100</v>
@@ -5748,10 +5748,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" t="n">
         <v>51</v>
-      </c>
-      <c r="B86" t="n">
-        <v>4</v>
       </c>
       <c r="C86" t="n">
         <v>36</v>
@@ -5812,10 +5812,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B87" t="n">
         <v>52</v>
-      </c>
-      <c r="B87" t="n">
-        <v>4</v>
       </c>
       <c r="C87" t="n">
         <v>93</v>
@@ -5876,10 +5876,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
+        <v>4</v>
+      </c>
+      <c r="B88" t="n">
         <v>53</v>
-      </c>
-      <c r="B88" t="n">
-        <v>4</v>
       </c>
       <c r="C88" t="n">
         <v>69</v>
@@ -5940,10 +5940,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B89" t="n">
         <v>54</v>
-      </c>
-      <c r="B89" t="n">
-        <v>4</v>
       </c>
       <c r="C89" t="n">
         <v>53</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
+        <v>4</v>
+      </c>
+      <c r="B90" t="n">
         <v>55</v>
-      </c>
-      <c r="B90" t="n">
-        <v>4</v>
       </c>
       <c r="C90" t="n">
         <v>100</v>
@@ -6068,10 +6068,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
+        <v>4</v>
+      </c>
+      <c r="B91" t="n">
         <v>62</v>
-      </c>
-      <c r="B91" t="n">
-        <v>4</v>
       </c>
       <c r="C91" t="n">
         <v>73</v>
@@ -6132,10 +6132,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
+        <v>4</v>
+      </c>
+      <c r="B92" t="n">
         <v>69</v>
-      </c>
-      <c r="B92" t="n">
-        <v>4</v>
       </c>
       <c r="C92" t="n">
         <v>55</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" t="n">
         <v>78</v>
-      </c>
-      <c r="B93" t="n">
-        <v>4</v>
       </c>
       <c r="C93" t="n">
         <v>2</v>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" t="n">
         <v>87</v>
-      </c>
-      <c r="B94" t="n">
-        <v>4</v>
       </c>
       <c r="C94" t="n">
         <v>78</v>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
+        <v>4</v>
+      </c>
+      <c r="B95" t="n">
         <v>89</v>
-      </c>
-      <c r="B95" t="n">
-        <v>4</v>
       </c>
       <c r="C95" t="n">
         <v>93</v>
@@ -6384,10 +6384,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B96" t="n">
         <v>92</v>
-      </c>
-      <c r="B96" t="n">
-        <v>4</v>
       </c>
       <c r="C96" t="n">
         <v>51</v>
@@ -6448,10 +6448,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
+        <v>4</v>
+      </c>
+      <c r="B97" t="n">
         <v>95</v>
-      </c>
-      <c r="B97" t="n">
-        <v>4</v>
       </c>
       <c r="C97" t="n">
         <v>93</v>
@@ -6512,10 +6512,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
+        <v>4</v>
+      </c>
+      <c r="B98" t="n">
         <v>99</v>
-      </c>
-      <c r="B98" t="n">
-        <v>4</v>
       </c>
       <c r="C98" t="n">
         <v>93</v>
@@ -6576,10 +6576,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
+        <v>4</v>
+      </c>
+      <c r="B99" t="n">
         <v>102</v>
-      </c>
-      <c r="B99" t="n">
-        <v>4</v>
       </c>
       <c r="C99" t="n">
         <v>53</v>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
+        <v>4</v>
+      </c>
+      <c r="B100" t="n">
         <v>109</v>
-      </c>
-      <c r="B100" t="n">
-        <v>4</v>
       </c>
       <c r="C100" t="n">
         <v>92</v>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
+        <v>4</v>
+      </c>
+      <c r="B101" t="n">
         <v>112</v>
-      </c>
-      <c r="B101" t="n">
-        <v>4</v>
       </c>
       <c r="C101" t="n">
         <v>71</v>
@@ -6768,10 +6768,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
+        <v>5</v>
+      </c>
+      <c r="B102" t="n">
         <v>4</v>
-      </c>
-      <c r="B102" t="n">
-        <v>5</v>
       </c>
       <c r="C102" t="n">
         <v>90</v>
@@ -6832,10 +6832,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
+        <v>5</v>
+      </c>
+      <c r="B103" t="n">
         <v>11</v>
-      </c>
-      <c r="B103" t="n">
-        <v>5</v>
       </c>
       <c r="C103" t="n">
         <v>80</v>
@@ -6896,10 +6896,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
+        <v>5</v>
+      </c>
+      <c r="B104" t="n">
         <v>12</v>
-      </c>
-      <c r="B104" t="n">
-        <v>5</v>
       </c>
       <c r="C104" t="n">
         <v>93</v>
@@ -6960,10 +6960,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
+        <v>5</v>
+      </c>
+      <c r="B105" t="n">
         <v>16</v>
-      </c>
-      <c r="B105" t="n">
-        <v>5</v>
       </c>
       <c r="C105" t="n">
         <v>35</v>
@@ -7024,10 +7024,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
+        <v>5</v>
+      </c>
+      <c r="B106" t="n">
         <v>22</v>
-      </c>
-      <c r="B106" t="n">
-        <v>5</v>
       </c>
       <c r="C106" t="n">
         <v>92</v>
@@ -7088,10 +7088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
+        <v>5</v>
+      </c>
+      <c r="B107" t="n">
         <v>24</v>
-      </c>
-      <c r="B107" t="n">
-        <v>5</v>
       </c>
       <c r="C107" t="n">
         <v>92</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
+        <v>6</v>
+      </c>
+      <c r="B108" t="n">
         <v>3</v>
-      </c>
-      <c r="B108" t="n">
-        <v>6</v>
       </c>
       <c r="C108" t="n">
         <v>12</v>
@@ -7216,10 +7216,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
+        <v>6</v>
+      </c>
+      <c r="B109" t="n">
         <v>8</v>
-      </c>
-      <c r="B109" t="n">
-        <v>6</v>
       </c>
       <c r="C109" t="n">
         <v>53</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
+        <v>6</v>
+      </c>
+      <c r="B110" t="n">
         <v>16</v>
-      </c>
-      <c r="B110" t="n">
-        <v>6</v>
       </c>
       <c r="C110" t="n">
         <v>51</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
+        <v>6</v>
+      </c>
+      <c r="B111" t="n">
         <v>21</v>
-      </c>
-      <c r="B111" t="n">
-        <v>6</v>
       </c>
       <c r="C111" t="n">
         <v>76</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
+        <v>6</v>
+      </c>
+      <c r="B112" t="n">
         <v>47</v>
-      </c>
-      <c r="B112" t="n">
-        <v>6</v>
       </c>
       <c r="C112" t="n">
         <v>76</v>
@@ -7472,10 +7472,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
+        <v>6</v>
+      </c>
+      <c r="B113" t="n">
         <v>50</v>
-      </c>
-      <c r="B113" t="n">
-        <v>6</v>
       </c>
       <c r="C113" t="n">
         <v>96</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
+        <v>6</v>
+      </c>
+      <c r="B114" t="n">
         <v>51</v>
-      </c>
-      <c r="B114" t="n">
-        <v>6</v>
       </c>
       <c r="C114" t="n">
         <v>38</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
+        <v>6</v>
+      </c>
+      <c r="B115" t="n">
         <v>59</v>
-      </c>
-      <c r="B115" t="n">
-        <v>6</v>
       </c>
       <c r="C115" t="n">
         <v>97</v>
@@ -7664,10 +7664,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
+        <v>6</v>
+      </c>
+      <c r="B116" t="n">
         <v>64</v>
-      </c>
-      <c r="B116" t="n">
-        <v>6</v>
       </c>
       <c r="C116" t="n">
         <v>80</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
+        <v>6</v>
+      </c>
+      <c r="B117" t="n">
         <v>72</v>
-      </c>
-      <c r="B117" t="n">
-        <v>6</v>
       </c>
       <c r="C117" t="n">
         <v>40</v>
@@ -7792,10 +7792,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
+        <v>6</v>
+      </c>
+      <c r="B118" t="n">
         <v>82</v>
-      </c>
-      <c r="B118" t="n">
-        <v>6</v>
       </c>
       <c r="C118" t="n">
         <v>60</v>
@@ -7856,10 +7856,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
+        <v>6</v>
+      </c>
+      <c r="B119" t="n">
         <v>83</v>
-      </c>
-      <c r="B119" t="n">
-        <v>6</v>
       </c>
       <c r="C119" t="n">
         <v>57</v>
@@ -7920,10 +7920,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
+        <v>6</v>
+      </c>
+      <c r="B120" t="n">
         <v>87</v>
-      </c>
-      <c r="B120" t="n">
-        <v>6</v>
       </c>
       <c r="C120" t="n">
         <v>74</v>
@@ -7984,10 +7984,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
+        <v>6</v>
+      </c>
+      <c r="B121" t="n">
         <v>88</v>
-      </c>
-      <c r="B121" t="n">
-        <v>6</v>
       </c>
       <c r="C121" t="n">
         <v>16</v>
@@ -8048,10 +8048,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
+        <v>6</v>
+      </c>
+      <c r="B122" t="n">
         <v>100</v>
-      </c>
-      <c r="B122" t="n">
-        <v>6</v>
       </c>
       <c r="C122" t="n">
         <v>35</v>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
+        <v>6</v>
+      </c>
+      <c r="B123" t="n">
         <v>109</v>
-      </c>
-      <c r="B123" t="n">
-        <v>6</v>
       </c>
       <c r="C123" t="n">
         <v>53</v>
@@ -8176,10 +8176,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
+        <v>6</v>
+      </c>
+      <c r="B124" t="n">
         <v>114</v>
-      </c>
-      <c r="B124" t="n">
-        <v>6</v>
       </c>
       <c r="C124" t="n">
         <v>33</v>
@@ -8240,10 +8240,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
+        <v>7</v>
+      </c>
+      <c r="B125" t="n">
         <v>1</v>
-      </c>
-      <c r="B125" t="n">
-        <v>7</v>
       </c>
       <c r="C125" t="n">
         <v>71</v>
@@ -8304,10 +8304,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
+        <v>7</v>
+      </c>
+      <c r="B126" t="n">
         <v>2</v>
-      </c>
-      <c r="B126" t="n">
-        <v>7</v>
       </c>
       <c r="C126" t="n">
         <v>6</v>
@@ -8368,10 +8368,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
+        <v>7</v>
+      </c>
+      <c r="B127" t="n">
         <v>8</v>
-      </c>
-      <c r="B127" t="n">
-        <v>7</v>
       </c>
       <c r="C127" t="n">
         <v>18</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
+        <v>7</v>
+      </c>
+      <c r="B128" t="n">
         <v>10</v>
-      </c>
-      <c r="B128" t="n">
-        <v>7</v>
       </c>
       <c r="C128" t="n">
         <v>6</v>
@@ -8496,10 +8496,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
+        <v>7</v>
+      </c>
+      <c r="B129" t="n">
         <v>11</v>
-      </c>
-      <c r="B129" t="n">
-        <v>7</v>
       </c>
       <c r="C129" t="n">
         <v>40</v>
@@ -8560,10 +8560,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
+        <v>7</v>
+      </c>
+      <c r="B130" t="n">
         <v>13</v>
-      </c>
-      <c r="B130" t="n">
-        <v>7</v>
       </c>
       <c r="C130" t="n">
         <v>17</v>
@@ -8624,10 +8624,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
+        <v>7</v>
+      </c>
+      <c r="B131" t="n">
         <v>19</v>
-      </c>
-      <c r="B131" t="n">
-        <v>7</v>
       </c>
       <c r="C131" t="n">
         <v>53</v>
@@ -8684,10 +8684,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
+        <v>7</v>
+      </c>
+      <c r="B132" t="n">
         <v>20</v>
-      </c>
-      <c r="B132" t="n">
-        <v>7</v>
       </c>
       <c r="C132" t="n">
         <v>90</v>
@@ -8748,10 +8748,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
+        <v>7</v>
+      </c>
+      <c r="B133" t="n">
         <v>21</v>
-      </c>
-      <c r="B133" t="n">
-        <v>7</v>
       </c>
       <c r="C133" t="n">
         <v>67</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
+        <v>7</v>
+      </c>
+      <c r="B134" t="n">
         <v>471</v>
-      </c>
-      <c r="B134" t="n">
-        <v>7</v>
       </c>
       <c r="C134" t="n">
         <v>13</v>
@@ -8876,10 +8876,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
+        <v>7</v>
+      </c>
+      <c r="B135" t="n">
         <v>24</v>
-      </c>
-      <c r="B135" t="n">
-        <v>7</v>
       </c>
       <c r="C135" t="n">
         <v>92</v>
@@ -8940,10 +8940,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
+        <v>7</v>
+      </c>
+      <c r="B136" t="n">
         <v>27</v>
-      </c>
-      <c r="B136" t="n">
-        <v>7</v>
       </c>
       <c r="C136" t="n">
         <v>97</v>
@@ -9004,10 +9004,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
+        <v>7</v>
+      </c>
+      <c r="B137" t="n">
         <v>31</v>
-      </c>
-      <c r="B137" t="n">
-        <v>7</v>
       </c>
       <c r="C137" t="n">
         <v>71</v>
@@ -9068,10 +9068,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
+        <v>7</v>
+      </c>
+      <c r="B138" t="n">
         <v>32</v>
-      </c>
-      <c r="B138" t="n">
-        <v>7</v>
       </c>
       <c r="C138" t="n">
         <v>92</v>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
+        <v>7</v>
+      </c>
+      <c r="B139" t="n">
         <v>33</v>
-      </c>
-      <c r="B139" t="n">
-        <v>7</v>
       </c>
       <c r="C139" t="n">
         <v>92</v>
@@ -9196,10 +9196,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
+        <v>7</v>
+      </c>
+      <c r="B140" t="n">
         <v>43</v>
-      </c>
-      <c r="B140" t="n">
-        <v>7</v>
       </c>
       <c r="C140" t="n">
         <v>97</v>
@@ -9260,10 +9260,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
+        <v>7</v>
+      </c>
+      <c r="B141" t="n">
         <v>47</v>
-      </c>
-      <c r="B141" t="n">
-        <v>7</v>
       </c>
       <c r="C141" t="n">
         <v>66</v>
@@ -9324,10 +9324,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
+        <v>7</v>
+      </c>
+      <c r="B142" t="n">
         <v>50</v>
-      </c>
-      <c r="B142" t="n">
-        <v>7</v>
       </c>
       <c r="C142" t="n">
         <v>93</v>
@@ -9388,10 +9388,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
+        <v>7</v>
+      </c>
+      <c r="B143" t="n">
         <v>51</v>
-      </c>
-      <c r="B143" t="n">
-        <v>7</v>
       </c>
       <c r="C143" t="n">
         <v>93</v>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
+        <v>7</v>
+      </c>
+      <c r="B144" t="n">
         <v>52</v>
-      </c>
-      <c r="B144" t="n">
-        <v>7</v>
       </c>
       <c r="C144" t="n">
         <v>38</v>
@@ -9516,10 +9516,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
+        <v>7</v>
+      </c>
+      <c r="B145" t="n">
         <v>58</v>
-      </c>
-      <c r="B145" t="n">
-        <v>7</v>
       </c>
       <c r="C145" t="n">
         <v>55</v>
@@ -9580,10 +9580,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
+        <v>7</v>
+      </c>
+      <c r="B146" t="n">
         <v>59</v>
-      </c>
-      <c r="B146" t="n">
-        <v>7</v>
       </c>
       <c r="C146" t="n">
         <v>80</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
+        <v>7</v>
+      </c>
+      <c r="B147" t="n">
         <v>62</v>
-      </c>
-      <c r="B147" t="n">
-        <v>7</v>
       </c>
       <c r="C147" t="n">
         <v>92</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
+        <v>7</v>
+      </c>
+      <c r="B148" t="n">
         <v>63</v>
-      </c>
-      <c r="B148" t="n">
-        <v>7</v>
       </c>
       <c r="C148" t="n">
         <v>41</v>
@@ -9768,10 +9768,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
+        <v>7</v>
+      </c>
+      <c r="B149" t="n">
         <v>64</v>
-      </c>
-      <c r="B149" t="n">
-        <v>7</v>
       </c>
       <c r="C149" t="n">
         <v>41</v>
@@ -9832,10 +9832,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
+        <v>7</v>
+      </c>
+      <c r="B150" t="n">
         <v>65</v>
-      </c>
-      <c r="B150" t="n">
-        <v>7</v>
       </c>
       <c r="C150" t="n">
         <v>57</v>
@@ -9892,10 +9892,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
+        <v>7</v>
+      </c>
+      <c r="B151" t="n">
         <v>71</v>
-      </c>
-      <c r="B151" t="n">
-        <v>7</v>
       </c>
       <c r="C151" t="n">
         <v>34</v>
@@ -9956,10 +9956,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
+        <v>7</v>
+      </c>
+      <c r="B152" t="n">
         <v>73</v>
-      </c>
-      <c r="B152" t="n">
-        <v>7</v>
       </c>
       <c r="C152" t="n">
         <v>34</v>
@@ -10020,10 +10020,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
+        <v>7</v>
+      </c>
+      <c r="B153" t="n">
         <v>78</v>
-      </c>
-      <c r="B153" t="n">
-        <v>7</v>
       </c>
       <c r="C153" t="n">
         <v>41</v>
@@ -10084,10 +10084,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
+        <v>7</v>
+      </c>
+      <c r="B154" t="n">
         <v>80</v>
-      </c>
-      <c r="B154" t="n">
-        <v>7</v>
       </c>
       <c r="C154" t="n">
         <v>55</v>
@@ -10148,10 +10148,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
+        <v>7</v>
+      </c>
+      <c r="B155" t="n">
         <v>81</v>
-      </c>
-      <c r="B155" t="n">
-        <v>7</v>
       </c>
       <c r="C155" t="n">
         <v>71</v>
@@ -10212,10 +10212,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
+        <v>7</v>
+      </c>
+      <c r="B156" t="n">
         <v>82</v>
-      </c>
-      <c r="B156" t="n">
-        <v>7</v>
       </c>
       <c r="C156" t="n">
         <v>28</v>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
+        <v>7</v>
+      </c>
+      <c r="B157" t="n">
         <v>83</v>
-      </c>
-      <c r="B157" t="n">
-        <v>7</v>
       </c>
       <c r="C157" t="n">
         <v>100</v>
@@ -10340,10 +10340,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
+        <v>7</v>
+      </c>
+      <c r="B158" t="n">
         <v>84</v>
-      </c>
-      <c r="B158" t="n">
-        <v>7</v>
       </c>
       <c r="C158" t="n">
         <v>100</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
+        <v>7</v>
+      </c>
+      <c r="B159" t="n">
         <v>86</v>
-      </c>
-      <c r="B159" t="n">
-        <v>7</v>
       </c>
       <c r="C159" t="n">
         <v>14</v>
@@ -10468,10 +10468,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
+        <v>7</v>
+      </c>
+      <c r="B160" t="n">
         <v>88</v>
-      </c>
-      <c r="B160" t="n">
-        <v>7</v>
       </c>
       <c r="C160" t="n">
         <v>92</v>
@@ -10528,10 +10528,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
+        <v>7</v>
+      </c>
+      <c r="B161" t="n">
         <v>90</v>
-      </c>
-      <c r="B161" t="n">
-        <v>7</v>
       </c>
       <c r="C161" t="n">
         <v>93</v>
@@ -10588,10 +10588,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
+        <v>7</v>
+      </c>
+      <c r="B162" t="n">
         <v>100</v>
-      </c>
-      <c r="B162" t="n">
-        <v>7</v>
       </c>
       <c r="C162" t="n">
         <v>41</v>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
+        <v>7</v>
+      </c>
+      <c r="B163" t="n">
         <v>101</v>
-      </c>
-      <c r="B163" t="n">
-        <v>7</v>
       </c>
       <c r="C163" t="n">
         <v>100</v>
@@ -10716,10 +10716,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
+        <v>7</v>
+      </c>
+      <c r="B164" t="n">
         <v>103</v>
-      </c>
-      <c r="B164" t="n">
-        <v>7</v>
       </c>
       <c r="C164" t="n">
         <v>93</v>
@@ -10780,10 +10780,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
+        <v>7</v>
+      </c>
+      <c r="B165" t="n">
         <v>104</v>
-      </c>
-      <c r="B165" t="n">
-        <v>7</v>
       </c>
       <c r="C165" t="n">
         <v>18</v>
@@ -10844,10 +10844,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
+        <v>7</v>
+      </c>
+      <c r="B166" t="n">
         <v>107</v>
-      </c>
-      <c r="B166" t="n">
-        <v>7</v>
       </c>
       <c r="C166" t="n">
         <v>55</v>
@@ -10904,10 +10904,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
+        <v>7</v>
+      </c>
+      <c r="B167" t="n">
         <v>110</v>
-      </c>
-      <c r="B167" t="n">
-        <v>7</v>
       </c>
       <c r="C167" t="n">
         <v>35</v>
@@ -10968,10 +10968,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
+        <v>7</v>
+      </c>
+      <c r="B168" t="n">
         <v>112</v>
-      </c>
-      <c r="B168" t="n">
-        <v>7</v>
       </c>
       <c r="C168" t="n">
         <v>92</v>
@@ -11032,10 +11032,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
+        <v>7</v>
+      </c>
+      <c r="B169" t="n">
         <v>120</v>
-      </c>
-      <c r="B169" t="n">
-        <v>7</v>
       </c>
       <c r="C169" t="n">
         <v>13</v>
@@ -11096,10 +11096,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
+        <v>7</v>
+      </c>
+      <c r="B170" t="n">
         <v>121</v>
-      </c>
-      <c r="B170" t="n">
-        <v>7</v>
       </c>
       <c r="C170" t="n">
         <v>77</v>
@@ -11160,10 +11160,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
+        <v>7</v>
+      </c>
+      <c r="B171" t="n">
         <v>122</v>
-      </c>
-      <c r="B171" t="n">
-        <v>7</v>
       </c>
       <c r="C171" t="n">
         <v>92</v>
@@ -11224,10 +11224,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
+        <v>7</v>
+      </c>
+      <c r="B172" t="n">
         <v>124</v>
-      </c>
-      <c r="B172" t="n">
-        <v>7</v>
       </c>
       <c r="C172" t="n">
         <v>52</v>
@@ -11288,10 +11288,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
+        <v>7</v>
+      </c>
+      <c r="B173" t="n">
         <v>130</v>
-      </c>
-      <c r="B173" t="n">
-        <v>7</v>
       </c>
       <c r="C173" t="n">
         <v>55</v>
@@ -11352,10 +11352,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
+        <v>7</v>
+      </c>
+      <c r="B174" t="n">
         <v>132</v>
-      </c>
-      <c r="B174" t="n">
-        <v>7</v>
       </c>
       <c r="C174" t="n">
         <v>44</v>
@@ -11416,10 +11416,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
+        <v>7</v>
+      </c>
+      <c r="B175" t="n">
         <v>133</v>
-      </c>
-      <c r="B175" t="n">
-        <v>7</v>
       </c>
       <c r="C175" t="n">
         <v>57</v>
@@ -11480,10 +11480,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
+        <v>7</v>
+      </c>
+      <c r="B176" t="n">
         <v>136</v>
-      </c>
-      <c r="B176" t="n">
-        <v>7</v>
       </c>
       <c r="C176" t="n">
         <v>75</v>
@@ -11544,10 +11544,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
+        <v>7</v>
+      </c>
+      <c r="B177" t="n">
         <v>147</v>
-      </c>
-      <c r="B177" t="n">
-        <v>7</v>
       </c>
       <c r="C177" t="n">
         <v>17</v>
@@ -11608,10 +11608,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
+        <v>7</v>
+      </c>
+      <c r="B178" t="n">
         <v>151</v>
-      </c>
-      <c r="B178" t="n">
-        <v>7</v>
       </c>
       <c r="C178" t="n">
         <v>51</v>
@@ -11672,10 +11672,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
+        <v>7</v>
+      </c>
+      <c r="B179" t="n">
         <v>160</v>
-      </c>
-      <c r="B179" t="n">
-        <v>7</v>
       </c>
       <c r="C179" t="n">
         <v>36</v>
@@ -11736,10 +11736,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
+        <v>7</v>
+      </c>
+      <c r="B180" t="n">
         <v>170</v>
-      </c>
-      <c r="B180" t="n">
-        <v>7</v>
       </c>
       <c r="C180" t="n">
         <v>81</v>
@@ -11800,10 +11800,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
+        <v>7</v>
+      </c>
+      <c r="B181" t="n">
         <v>177</v>
-      </c>
-      <c r="B181" t="n">
-        <v>7</v>
       </c>
       <c r="C181" t="n">
         <v>57</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
+        <v>7</v>
+      </c>
+      <c r="B182" t="n">
         <v>183</v>
-      </c>
-      <c r="B182" t="n">
-        <v>7</v>
       </c>
       <c r="C182" t="n">
         <v>18</v>
@@ -11928,10 +11928,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
+        <v>7</v>
+      </c>
+      <c r="B183" t="n">
         <v>185</v>
-      </c>
-      <c r="B183" t="n">
-        <v>7</v>
       </c>
       <c r="C183" t="n">
         <v>18</v>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
+        <v>7</v>
+      </c>
+      <c r="B184" t="n">
         <v>191</v>
-      </c>
-      <c r="B184" t="n">
-        <v>7</v>
       </c>
       <c r="C184" t="n">
         <v>92</v>
@@ -12056,10 +12056,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
+        <v>7</v>
+      </c>
+      <c r="B185" t="n">
         <v>199</v>
-      </c>
-      <c r="B185" t="n">
-        <v>7</v>
       </c>
       <c r="C185" t="n">
         <v>57</v>
@@ -12120,10 +12120,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
+        <v>7</v>
+      </c>
+      <c r="B186" t="n">
         <v>204</v>
-      </c>
-      <c r="B186" t="n">
-        <v>7</v>
       </c>
       <c r="C186" t="n">
         <v>57</v>
@@ -12184,10 +12184,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
+        <v>7</v>
+      </c>
+      <c r="B187" t="n">
         <v>209</v>
-      </c>
-      <c r="B187" t="n">
-        <v>7</v>
       </c>
       <c r="C187" t="n">
         <v>85</v>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
+        <v>7</v>
+      </c>
+      <c r="B188" t="n">
         <v>214</v>
-      </c>
-      <c r="B188" t="n">
-        <v>7</v>
       </c>
       <c r="C188" t="n">
         <v>53</v>
@@ -12312,10 +12312,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
+        <v>7</v>
+      </c>
+      <c r="B189" t="n">
         <v>220</v>
-      </c>
-      <c r="B189" t="n">
-        <v>7</v>
       </c>
       <c r="C189" t="n">
         <v>2</v>
@@ -12376,10 +12376,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
+        <v>7</v>
+      </c>
+      <c r="B190" t="n">
         <v>233</v>
-      </c>
-      <c r="B190" t="n">
-        <v>7</v>
       </c>
       <c r="C190" t="n">
         <v>90</v>
@@ -12440,10 +12440,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
+        <v>7</v>
+      </c>
+      <c r="B191" t="n">
         <v>247</v>
-      </c>
-      <c r="B191" t="n">
-        <v>7</v>
       </c>
       <c r="C191" t="n">
         <v>57</v>
@@ -12504,10 +12504,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
+        <v>7</v>
+      </c>
+      <c r="B192" t="n">
         <v>249</v>
-      </c>
-      <c r="B192" t="n">
-        <v>7</v>
       </c>
       <c r="C192" t="n">
         <v>18</v>
@@ -12568,10 +12568,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
+        <v>7</v>
+      </c>
+      <c r="B193" t="n">
         <v>250</v>
-      </c>
-      <c r="B193" t="n">
-        <v>7</v>
       </c>
       <c r="C193" t="n">
         <v>44</v>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
+        <v>7</v>
+      </c>
+      <c r="B194" t="n">
         <v>251</v>
-      </c>
-      <c r="B194" t="n">
-        <v>7</v>
       </c>
       <c r="C194" t="n">
         <v>92</v>
@@ -12696,10 +12696,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
+        <v>7</v>
+      </c>
+      <c r="B195" t="n">
         <v>255</v>
-      </c>
-      <c r="B195" t="n">
-        <v>7</v>
       </c>
       <c r="C195" t="n">
         <v>35</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
+        <v>7</v>
+      </c>
+      <c r="B196" t="n">
         <v>256</v>
-      </c>
-      <c r="B196" t="n">
-        <v>7</v>
       </c>
       <c r="C196" t="n">
         <v>45</v>
@@ -12824,10 +12824,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
+        <v>7</v>
+      </c>
+      <c r="B197" t="n">
         <v>268</v>
-      </c>
-      <c r="B197" t="n">
-        <v>7</v>
       </c>
       <c r="C197" t="n">
         <v>57</v>
@@ -12884,10 +12884,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
+        <v>7</v>
+      </c>
+      <c r="B198" t="n">
         <v>269</v>
-      </c>
-      <c r="B198" t="n">
-        <v>7</v>
       </c>
       <c r="C198" t="n">
         <v>36</v>
@@ -12948,10 +12948,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
+        <v>7</v>
+      </c>
+      <c r="B199" t="n">
         <v>275</v>
-      </c>
-      <c r="B199" t="n">
-        <v>7</v>
       </c>
       <c r="C199" t="n">
         <v>57</v>
@@ -13012,10 +13012,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
+        <v>7</v>
+      </c>
+      <c r="B200" t="n">
         <v>289</v>
-      </c>
-      <c r="B200" t="n">
-        <v>7</v>
       </c>
       <c r="C200" t="n">
         <v>71</v>
@@ -13072,10 +13072,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
+        <v>7</v>
+      </c>
+      <c r="B201" t="n">
         <v>293</v>
-      </c>
-      <c r="B201" t="n">
-        <v>7</v>
       </c>
       <c r="C201" t="n">
         <v>18</v>
@@ -13136,10 +13136,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
+        <v>7</v>
+      </c>
+      <c r="B202" t="n">
         <v>300</v>
-      </c>
-      <c r="B202" t="n">
-        <v>7</v>
       </c>
       <c r="C202" t="n">
         <v>77</v>
@@ -13200,10 +13200,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
+        <v>7</v>
+      </c>
+      <c r="B203" t="n">
         <v>301</v>
-      </c>
-      <c r="B203" t="n">
-        <v>7</v>
       </c>
       <c r="C203" t="n">
         <v>57</v>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
+        <v>7</v>
+      </c>
+      <c r="B204" t="n">
         <v>302</v>
-      </c>
-      <c r="B204" t="n">
-        <v>7</v>
       </c>
       <c r="C204" t="n">
         <v>57</v>
@@ -13328,10 +13328,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
+        <v>7</v>
+      </c>
+      <c r="B205" t="n">
         <v>305</v>
-      </c>
-      <c r="B205" t="n">
-        <v>7</v>
       </c>
       <c r="C205" t="n">
         <v>38</v>
@@ -13392,10 +13392,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
+        <v>7</v>
+      </c>
+      <c r="B206" t="n">
         <v>311</v>
-      </c>
-      <c r="B206" t="n">
-        <v>7</v>
       </c>
       <c r="C206" t="n">
         <v>92</v>
@@ -13456,10 +13456,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
+        <v>7</v>
+      </c>
+      <c r="B207" t="n">
         <v>325</v>
-      </c>
-      <c r="B207" t="n">
-        <v>7</v>
       </c>
       <c r="C207" t="n">
         <v>57</v>
@@ -13520,10 +13520,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
+        <v>7</v>
+      </c>
+      <c r="B208" t="n">
         <v>328</v>
-      </c>
-      <c r="B208" t="n">
-        <v>7</v>
       </c>
       <c r="C208" t="n">
         <v>87</v>
@@ -13580,10 +13580,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
+        <v>7</v>
+      </c>
+      <c r="B209" t="n">
         <v>335</v>
-      </c>
-      <c r="B209" t="n">
-        <v>7</v>
       </c>
       <c r="C209" t="n">
         <v>54</v>
@@ -13644,10 +13644,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
+        <v>7</v>
+      </c>
+      <c r="B210" t="n">
         <v>336</v>
-      </c>
-      <c r="B210" t="n">
-        <v>7</v>
       </c>
       <c r="C210" t="n">
         <v>55</v>
@@ -13708,10 +13708,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
+        <v>7</v>
+      </c>
+      <c r="B211" t="n">
         <v>341</v>
-      </c>
-      <c r="B211" t="n">
-        <v>7</v>
       </c>
       <c r="C211" t="n">
         <v>6</v>
@@ -13772,10 +13772,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
+        <v>7</v>
+      </c>
+      <c r="B212" t="n">
         <v>344</v>
-      </c>
-      <c r="B212" t="n">
-        <v>7</v>
       </c>
       <c r="C212" t="n">
         <v>36</v>
@@ -13836,10 +13836,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
+        <v>7</v>
+      </c>
+      <c r="B213" t="n">
         <v>348</v>
-      </c>
-      <c r="B213" t="n">
-        <v>7</v>
       </c>
       <c r="C213" t="n">
         <v>92</v>
@@ -13900,10 +13900,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
+        <v>7</v>
+      </c>
+      <c r="B214" t="n">
         <v>350</v>
-      </c>
-      <c r="B214" t="n">
-        <v>7</v>
       </c>
       <c r="C214" t="n">
         <v>57</v>
@@ -13964,10 +13964,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
+        <v>7</v>
+      </c>
+      <c r="B215" t="n">
         <v>351</v>
-      </c>
-      <c r="B215" t="n">
-        <v>7</v>
       </c>
       <c r="C215" t="n">
         <v>71</v>
@@ -14028,10 +14028,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
+        <v>7</v>
+      </c>
+      <c r="B216" t="n">
         <v>361</v>
-      </c>
-      <c r="B216" t="n">
-        <v>7</v>
       </c>
       <c r="C216" t="n">
         <v>57</v>
@@ -14092,10 +14092,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
+        <v>7</v>
+      </c>
+      <c r="B217" t="n">
         <v>369</v>
-      </c>
-      <c r="B217" t="n">
-        <v>7</v>
       </c>
       <c r="C217" t="n">
         <v>40</v>
@@ -14156,10 +14156,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
+        <v>7</v>
+      </c>
+      <c r="B218" t="n">
         <v>372</v>
-      </c>
-      <c r="B218" t="n">
-        <v>7</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -14220,10 +14220,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
+        <v>7</v>
+      </c>
+      <c r="B219" t="n">
         <v>377</v>
-      </c>
-      <c r="B219" t="n">
-        <v>7</v>
       </c>
       <c r="C219" t="n">
         <v>75</v>
@@ -14284,10 +14284,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
+        <v>7</v>
+      </c>
+      <c r="B220" t="n">
         <v>378</v>
-      </c>
-      <c r="B220" t="n">
-        <v>7</v>
       </c>
       <c r="C220" t="n">
         <v>6</v>
@@ -14348,10 +14348,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
+        <v>7</v>
+      </c>
+      <c r="B221" t="n">
         <v>379</v>
-      </c>
-      <c r="B221" t="n">
-        <v>7</v>
       </c>
       <c r="C221" t="n">
         <v>92</v>
@@ -14412,10 +14412,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
+        <v>7</v>
+      </c>
+      <c r="B222" t="n">
         <v>390</v>
-      </c>
-      <c r="B222" t="n">
-        <v>7</v>
       </c>
       <c r="C222" t="n">
         <v>79</v>
@@ -14476,10 +14476,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
+        <v>7</v>
+      </c>
+      <c r="B223" t="n">
         <v>391</v>
-      </c>
-      <c r="B223" t="n">
-        <v>7</v>
       </c>
       <c r="C223" t="n">
         <v>100</v>
@@ -14540,10 +14540,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
+        <v>7</v>
+      </c>
+      <c r="B224" t="n">
         <v>392</v>
-      </c>
-      <c r="B224" t="n">
-        <v>7</v>
       </c>
       <c r="C224" t="n">
         <v>18</v>
@@ -14604,10 +14604,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
+        <v>7</v>
+      </c>
+      <c r="B225" t="n">
         <v>393</v>
-      </c>
-      <c r="B225" t="n">
-        <v>7</v>
       </c>
       <c r="C225" t="n">
         <v>71</v>
@@ -14668,10 +14668,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
+        <v>7</v>
+      </c>
+      <c r="B226" t="n">
         <v>394</v>
-      </c>
-      <c r="B226" t="n">
-        <v>7</v>
       </c>
       <c r="C226" t="n">
         <v>100</v>
@@ -14732,10 +14732,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
+        <v>7</v>
+      </c>
+      <c r="B227" t="n">
         <v>396</v>
-      </c>
-      <c r="B227" t="n">
-        <v>7</v>
       </c>
       <c r="C227" t="n">
         <v>93</v>
@@ -14792,10 +14792,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
+        <v>7</v>
+      </c>
+      <c r="B228" t="n">
         <v>402</v>
-      </c>
-      <c r="B228" t="n">
-        <v>7</v>
       </c>
       <c r="C228" t="n">
         <v>100</v>
@@ -14856,10 +14856,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
+        <v>7</v>
+      </c>
+      <c r="B229" t="n">
         <v>412</v>
-      </c>
-      <c r="B229" t="n">
-        <v>7</v>
       </c>
       <c r="C229" t="n">
         <v>13</v>
@@ -14916,10 +14916,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
+        <v>7</v>
+      </c>
+      <c r="B230" t="n">
         <v>440</v>
-      </c>
-      <c r="B230" t="n">
-        <v>7</v>
       </c>
       <c r="C230" t="n">
         <v>36</v>
@@ -14976,10 +14976,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
+        <v>7</v>
+      </c>
+      <c r="B231" t="n">
         <v>450</v>
-      </c>
-      <c r="B231" t="n">
-        <v>7</v>
       </c>
       <c r="C231" t="n">
         <v>2</v>
@@ -15040,10 +15040,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
+        <v>7</v>
+      </c>
+      <c r="B232" t="n">
         <v>457</v>
-      </c>
-      <c r="B232" t="n">
-        <v>7</v>
       </c>
       <c r="C232" t="n">
         <v>13</v>
@@ -15104,10 +15104,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
+        <v>7</v>
+      </c>
+      <c r="B233" t="n">
         <v>460</v>
-      </c>
-      <c r="B233" t="n">
-        <v>7</v>
       </c>
       <c r="C233" t="n">
         <v>7</v>
@@ -15168,10 +15168,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
+        <v>7</v>
+      </c>
+      <c r="B234" t="n">
         <v>462</v>
-      </c>
-      <c r="B234" t="n">
-        <v>7</v>
       </c>
       <c r="C234" t="n">
         <v>66</v>
@@ -15232,10 +15232,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
+        <v>7</v>
+      </c>
+      <c r="B235" t="n">
         <v>466</v>
-      </c>
-      <c r="B235" t="n">
-        <v>7</v>
       </c>
       <c r="C235" t="n">
         <v>7</v>
@@ -15296,10 +15296,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
+        <v>7</v>
+      </c>
+      <c r="B236" t="n">
         <v>467</v>
-      </c>
-      <c r="B236" t="n">
-        <v>7</v>
       </c>
       <c r="C236" t="n">
         <v>52</v>
@@ -15356,10 +15356,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
+        <v>7</v>
+      </c>
+      <c r="B237" t="n">
         <v>470</v>
-      </c>
-      <c r="B237" t="n">
-        <v>7</v>
       </c>
       <c r="C237" t="n">
         <v>36</v>
@@ -15420,10 +15420,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
+        <v>8</v>
+      </c>
+      <c r="B238" t="n">
         <v>5</v>
-      </c>
-      <c r="B238" t="n">
-        <v>8</v>
       </c>
       <c r="C238" t="n">
         <v>80</v>
@@ -15484,10 +15484,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
+        <v>8</v>
+      </c>
+      <c r="B239" t="n">
         <v>7</v>
-      </c>
-      <c r="B239" t="n">
-        <v>8</v>
       </c>
       <c r="C239" t="n">
         <v>13</v>
@@ -15548,10 +15548,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
+        <v>8</v>
+      </c>
+      <c r="B240" t="n">
         <v>9</v>
-      </c>
-      <c r="B240" t="n">
-        <v>8</v>
       </c>
       <c r="C240" t="n">
         <v>14</v>
@@ -15612,10 +15612,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
+        <v>8</v>
+      </c>
+      <c r="B241" t="n">
         <v>15</v>
-      </c>
-      <c r="B241" t="n">
-        <v>8</v>
       </c>
       <c r="C241" t="n">
         <v>11</v>
@@ -15676,10 +15676,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
+        <v>8</v>
+      </c>
+      <c r="B242" t="n">
         <v>23</v>
-      </c>
-      <c r="B242" t="n">
-        <v>8</v>
       </c>
       <c r="C242" t="n">
         <v>51</v>
@@ -15740,10 +15740,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
+        <v>8</v>
+      </c>
+      <c r="B243" t="n">
         <v>25</v>
-      </c>
-      <c r="B243" t="n">
-        <v>8</v>
       </c>
       <c r="C243" t="n">
         <v>57</v>
@@ -15804,10 +15804,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
+        <v>8</v>
+      </c>
+      <c r="B244" t="n">
         <v>29</v>
-      </c>
-      <c r="B244" t="n">
-        <v>8</v>
       </c>
       <c r="C244" t="n">
         <v>58</v>
@@ -15868,10 +15868,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
+        <v>8</v>
+      </c>
+      <c r="B245" t="n">
         <v>31</v>
-      </c>
-      <c r="B245" t="n">
-        <v>8</v>
       </c>
       <c r="C245" t="n">
         <v>4</v>
@@ -15932,10 +15932,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
+        <v>8</v>
+      </c>
+      <c r="B246" t="n">
         <v>32</v>
-      </c>
-      <c r="B246" t="n">
-        <v>8</v>
       </c>
       <c r="C246" t="n">
         <v>71</v>
@@ -15996,10 +15996,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
+        <v>8</v>
+      </c>
+      <c r="B247" t="n">
         <v>35</v>
-      </c>
-      <c r="B247" t="n">
-        <v>8</v>
       </c>
       <c r="C247" t="n">
         <v>77</v>
@@ -16060,10 +16060,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
+        <v>8</v>
+      </c>
+      <c r="B248" t="n">
         <v>36</v>
-      </c>
-      <c r="B248" t="n">
-        <v>8</v>
       </c>
       <c r="C248" t="n">
         <v>76</v>
@@ -16124,10 +16124,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
+        <v>8</v>
+      </c>
+      <c r="B249" t="n">
         <v>37</v>
-      </c>
-      <c r="B249" t="n">
-        <v>8</v>
       </c>
       <c r="C249" t="n">
         <v>35</v>
@@ -16184,10 +16184,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
+        <v>8</v>
+      </c>
+      <c r="B250" t="n">
         <v>38</v>
-      </c>
-      <c r="B250" t="n">
-        <v>8</v>
       </c>
       <c r="C250" t="n">
         <v>55</v>
@@ -16248,10 +16248,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
+        <v>8</v>
+      </c>
+      <c r="B251" t="n">
         <v>39</v>
-      </c>
-      <c r="B251" t="n">
-        <v>8</v>
       </c>
       <c r="C251" t="n">
         <v>100</v>
@@ -16312,10 +16312,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
+        <v>8</v>
+      </c>
+      <c r="B252" t="n">
         <v>43</v>
-      </c>
-      <c r="B252" t="n">
-        <v>8</v>
       </c>
       <c r="C252" t="n">
         <v>92</v>
@@ -16376,10 +16376,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
+        <v>8</v>
+      </c>
+      <c r="B253" t="n">
         <v>48</v>
-      </c>
-      <c r="B253" t="n">
-        <v>8</v>
       </c>
       <c r="C253" t="n">
         <v>55</v>
@@ -16440,10 +16440,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
+        <v>8</v>
+      </c>
+      <c r="B254" t="n">
         <v>56</v>
-      </c>
-      <c r="B254" t="n">
-        <v>8</v>
       </c>
       <c r="C254" t="n">
         <v>80</v>
@@ -16504,10 +16504,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
+        <v>8</v>
+      </c>
+      <c r="B255" t="n">
         <v>57</v>
-      </c>
-      <c r="B255" t="n">
-        <v>8</v>
       </c>
       <c r="C255" t="n">
         <v>93</v>
@@ -16568,10 +16568,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
+        <v>8</v>
+      </c>
+      <c r="B256" t="n">
         <v>58</v>
-      </c>
-      <c r="B256" t="n">
-        <v>8</v>
       </c>
       <c r="C256" t="n">
         <v>36</v>
@@ -16632,10 +16632,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
+        <v>8</v>
+      </c>
+      <c r="B257" t="n">
         <v>62</v>
-      </c>
-      <c r="B257" t="n">
-        <v>8</v>
       </c>
       <c r="C257" t="n">
         <v>51</v>
@@ -16696,10 +16696,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
+        <v>8</v>
+      </c>
+      <c r="B258" t="n">
         <v>63</v>
-      </c>
-      <c r="B258" t="n">
-        <v>8</v>
       </c>
       <c r="C258" t="n">
         <v>80</v>
@@ -16760,10 +16760,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
+        <v>8</v>
+      </c>
+      <c r="B259" t="n">
         <v>64</v>
-      </c>
-      <c r="B259" t="n">
-        <v>8</v>
       </c>
       <c r="C259" t="n">
         <v>11</v>
@@ -16824,10 +16824,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
+        <v>8</v>
+      </c>
+      <c r="B260" t="n">
         <v>66</v>
-      </c>
-      <c r="B260" t="n">
-        <v>8</v>
       </c>
       <c r="C260" t="n">
         <v>55</v>
@@ -16888,10 +16888,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
+        <v>8</v>
+      </c>
+      <c r="B261" t="n">
         <v>69</v>
-      </c>
-      <c r="B261" t="n">
-        <v>8</v>
       </c>
       <c r="C261" t="n">
         <v>93</v>
@@ -16952,10 +16952,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
+        <v>8</v>
+      </c>
+      <c r="B262" t="n">
         <v>74</v>
-      </c>
-      <c r="B262" t="n">
-        <v>8</v>
       </c>
       <c r="C262" t="n">
         <v>96</v>
@@ -17016,10 +17016,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
+        <v>8</v>
+      </c>
+      <c r="B263" t="n">
         <v>79</v>
-      </c>
-      <c r="B263" t="n">
-        <v>8</v>
       </c>
       <c r="C263" t="n">
         <v>80</v>
@@ -17080,10 +17080,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
+        <v>8</v>
+      </c>
+      <c r="B264" t="n">
         <v>80</v>
-      </c>
-      <c r="B264" t="n">
-        <v>8</v>
       </c>
       <c r="C264" t="n">
         <v>41</v>
@@ -17140,10 +17140,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
+        <v>9</v>
+      </c>
+      <c r="B265" t="n">
         <v>4</v>
-      </c>
-      <c r="B265" t="n">
-        <v>9</v>
       </c>
       <c r="C265" t="n">
         <v>66</v>
@@ -17204,10 +17204,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
+        <v>9</v>
+      </c>
+      <c r="B266" t="n">
         <v>7</v>
-      </c>
-      <c r="B266" t="n">
-        <v>9</v>
       </c>
       <c r="C266" t="n">
         <v>80</v>
@@ -17268,10 +17268,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
+        <v>9</v>
+      </c>
+      <c r="B267" t="n">
         <v>11</v>
-      </c>
-      <c r="B267" t="n">
-        <v>9</v>
       </c>
       <c r="C267" t="n">
         <v>61</v>
@@ -17332,10 +17332,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
+        <v>9</v>
+      </c>
+      <c r="B268" t="n">
         <v>14</v>
-      </c>
-      <c r="B268" t="n">
-        <v>9</v>
       </c>
       <c r="C268" t="n">
         <v>97</v>
@@ -17396,10 +17396,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
+        <v>9</v>
+      </c>
+      <c r="B269" t="n">
         <v>15</v>
-      </c>
-      <c r="B269" t="n">
-        <v>9</v>
       </c>
       <c r="C269" t="n">
         <v>92</v>
@@ -17460,10 +17460,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
+        <v>9</v>
+      </c>
+      <c r="B270" t="n">
         <v>16</v>
-      </c>
-      <c r="B270" t="n">
-        <v>9</v>
       </c>
       <c r="C270" t="n">
         <v>93</v>
@@ -17524,10 +17524,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
+        <v>9</v>
+      </c>
+      <c r="B271" t="n">
         <v>17</v>
-      </c>
-      <c r="B271" t="n">
-        <v>9</v>
       </c>
       <c r="C271" t="n">
         <v>38</v>
@@ -17588,10 +17588,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
+        <v>9</v>
+      </c>
+      <c r="B272" t="n">
         <v>20</v>
-      </c>
-      <c r="B272" t="n">
-        <v>9</v>
       </c>
       <c r="C272" t="n">
         <v>18</v>
@@ -17652,10 +17652,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
+        <v>9</v>
+      </c>
+      <c r="B273" t="n">
         <v>21</v>
-      </c>
-      <c r="B273" t="n">
-        <v>9</v>
       </c>
       <c r="C273" t="n">
         <v>60</v>
@@ -17716,10 +17716,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
+        <v>9</v>
+      </c>
+      <c r="B274" t="n">
         <v>22</v>
-      </c>
-      <c r="B274" t="n">
-        <v>9</v>
       </c>
       <c r="C274" t="n">
         <v>21</v>
@@ -17780,10 +17780,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
+        <v>9</v>
+      </c>
+      <c r="B275" t="n">
         <v>23</v>
-      </c>
-      <c r="B275" t="n">
-        <v>9</v>
       </c>
       <c r="C275" t="n">
         <v>8</v>
@@ -17844,10 +17844,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
+        <v>9</v>
+      </c>
+      <c r="B276" t="n">
         <v>27</v>
-      </c>
-      <c r="B276" t="n">
-        <v>9</v>
       </c>
       <c r="C276" t="n">
         <v>78</v>
@@ -17908,10 +17908,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
+        <v>9</v>
+      </c>
+      <c r="B277" t="n">
         <v>30</v>
-      </c>
-      <c r="B277" t="n">
-        <v>9</v>
       </c>
       <c r="C277" t="n">
         <v>92</v>
@@ -17972,10 +17972,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
+        <v>9</v>
+      </c>
+      <c r="B278" t="n">
         <v>31</v>
-      </c>
-      <c r="B278" t="n">
-        <v>9</v>
       </c>
       <c r="C278" t="n">
         <v>18</v>
@@ -18036,10 +18036,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
+        <v>9</v>
+      </c>
+      <c r="B279" t="n">
         <v>32</v>
-      </c>
-      <c r="B279" t="n">
-        <v>9</v>
       </c>
       <c r="C279" t="n">
         <v>57</v>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
+        <v>10</v>
+      </c>
+      <c r="B280" t="n">
         <v>3</v>
-      </c>
-      <c r="B280" t="n">
-        <v>10</v>
       </c>
       <c r="C280" t="n">
         <v>71</v>
@@ -18160,10 +18160,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
+        <v>10</v>
+      </c>
+      <c r="B281" t="n">
         <v>4</v>
-      </c>
-      <c r="B281" t="n">
-        <v>10</v>
       </c>
       <c r="C281" t="n">
         <v>38</v>
@@ -18224,10 +18224,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
+        <v>10</v>
+      </c>
+      <c r="B282" t="n">
         <v>7</v>
-      </c>
-      <c r="B282" t="n">
-        <v>10</v>
       </c>
       <c r="C282" t="n">
         <v>38</v>
@@ -18348,10 +18348,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
+        <v>10</v>
+      </c>
+      <c r="B284" t="n">
         <v>13</v>
-      </c>
-      <c r="B284" t="n">
-        <v>10</v>
       </c>
       <c r="C284" t="n">
         <v>69</v>
@@ -18412,10 +18412,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
+        <v>10</v>
+      </c>
+      <c r="B285" t="n">
         <v>15</v>
-      </c>
-      <c r="B285" t="n">
-        <v>10</v>
       </c>
       <c r="C285" t="n">
         <v>93</v>
@@ -18476,10 +18476,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
+        <v>10</v>
+      </c>
+      <c r="B286" t="n">
         <v>17</v>
-      </c>
-      <c r="B286" t="n">
-        <v>10</v>
       </c>
       <c r="C286" t="n">
         <v>10</v>
@@ -18540,10 +18540,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
+        <v>10</v>
+      </c>
+      <c r="B287" t="n">
         <v>19</v>
-      </c>
-      <c r="B287" t="n">
-        <v>10</v>
       </c>
       <c r="C287" t="n">
         <v>2</v>
@@ -18600,10 +18600,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
+        <v>10</v>
+      </c>
+      <c r="B288" t="n">
         <v>21</v>
-      </c>
-      <c r="B288" t="n">
-        <v>10</v>
       </c>
       <c r="C288" t="n">
         <v>70</v>
@@ -18664,10 +18664,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
+        <v>10</v>
+      </c>
+      <c r="B289" t="n">
         <v>26</v>
-      </c>
-      <c r="B289" t="n">
-        <v>10</v>
       </c>
       <c r="C289" t="n">
         <v>93</v>
@@ -18728,10 +18728,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
+        <v>10</v>
+      </c>
+      <c r="B290" t="n">
         <v>28</v>
-      </c>
-      <c r="B290" t="n">
-        <v>10</v>
       </c>
       <c r="C290" t="n">
         <v>94</v>
@@ -18792,10 +18792,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
+        <v>10</v>
+      </c>
+      <c r="B291" t="n">
         <v>30</v>
-      </c>
-      <c r="B291" t="n">
-        <v>10</v>
       </c>
       <c r="C291" t="n">
         <v>93</v>
@@ -18856,10 +18856,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
+        <v>10</v>
+      </c>
+      <c r="B292" t="n">
         <v>32</v>
-      </c>
-      <c r="B292" t="n">
-        <v>10</v>
       </c>
       <c r="C292" t="n">
         <v>89</v>
@@ -18920,10 +18920,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
+        <v>10</v>
+      </c>
+      <c r="B293" t="n">
         <v>35</v>
-      </c>
-      <c r="B293" t="n">
-        <v>10</v>
       </c>
       <c r="C293" t="n">
         <v>96</v>
@@ -18984,10 +18984,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
+        <v>10</v>
+      </c>
+      <c r="B294" t="n">
         <v>40</v>
-      </c>
-      <c r="B294" t="n">
-        <v>10</v>
       </c>
       <c r="C294" t="n">
         <v>55</v>
@@ -19048,10 +19048,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
+        <v>10</v>
+      </c>
+      <c r="B295" t="n">
         <v>41</v>
-      </c>
-      <c r="B295" t="n">
-        <v>10</v>
       </c>
       <c r="C295" t="n">
         <v>33</v>
@@ -19112,10 +19112,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
+        <v>10</v>
+      </c>
+      <c r="B296" t="n">
         <v>44</v>
-      </c>
-      <c r="B296" t="n">
-        <v>10</v>
       </c>
       <c r="C296" t="n">
         <v>93</v>
@@ -19176,10 +19176,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
+        <v>10</v>
+      </c>
+      <c r="B297" t="n">
         <v>47</v>
-      </c>
-      <c r="B297" t="n">
-        <v>10</v>
       </c>
       <c r="C297" t="n">
         <v>51</v>
@@ -19240,10 +19240,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
+        <v>10</v>
+      </c>
+      <c r="B298" t="n">
         <v>49</v>
-      </c>
-      <c r="B298" t="n">
-        <v>10</v>
       </c>
       <c r="C298" t="n">
         <v>94</v>
@@ -19300,10 +19300,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
+        <v>11</v>
+      </c>
+      <c r="B299" t="n">
         <v>1</v>
-      </c>
-      <c r="B299" t="n">
-        <v>11</v>
       </c>
       <c r="C299" t="n">
         <v>18</v>
@@ -19364,10 +19364,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
+        <v>11</v>
+      </c>
+      <c r="B300" t="n">
         <v>12</v>
-      </c>
-      <c r="B300" t="n">
-        <v>11</v>
       </c>
       <c r="C300" t="n">
         <v>92</v>
@@ -19424,10 +19424,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
+        <v>11</v>
+      </c>
+      <c r="B301" t="n">
         <v>14</v>
-      </c>
-      <c r="B301" t="n">
-        <v>11</v>
       </c>
       <c r="C301" t="n">
         <v>20</v>
@@ -19488,10 +19488,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
+        <v>11</v>
+      </c>
+      <c r="B302" t="n">
         <v>20</v>
-      </c>
-      <c r="B302" t="n">
-        <v>11</v>
       </c>
       <c r="C302" t="n">
         <v>23</v>
@@ -19552,10 +19552,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
+        <v>11</v>
+      </c>
+      <c r="B303" t="n">
         <v>37</v>
-      </c>
-      <c r="B303" t="n">
-        <v>11</v>
       </c>
       <c r="C303" t="n">
         <v>53</v>
@@ -19616,10 +19616,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
+        <v>11</v>
+      </c>
+      <c r="B304" t="n">
         <v>39</v>
-      </c>
-      <c r="B304" t="n">
-        <v>11</v>
       </c>
       <c r="C304" t="n">
         <v>55</v>
@@ -19680,10 +19680,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
+        <v>11</v>
+      </c>
+      <c r="B305" t="n">
         <v>48</v>
-      </c>
-      <c r="B305" t="n">
-        <v>11</v>
       </c>
       <c r="C305" t="n">
         <v>6</v>
@@ -19744,10 +19744,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
+        <v>11</v>
+      </c>
+      <c r="B306" t="n">
         <v>50</v>
-      </c>
-      <c r="B306" t="n">
-        <v>11</v>
       </c>
       <c r="C306" t="n">
         <v>82</v>
@@ -19808,10 +19808,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
+        <v>11</v>
+      </c>
+      <c r="B307" t="n">
         <v>52</v>
-      </c>
-      <c r="B307" t="n">
-        <v>11</v>
       </c>
       <c r="C307" t="n">
         <v>13</v>
@@ -19872,10 +19872,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
+        <v>11</v>
+      </c>
+      <c r="B308" t="n">
         <v>53</v>
-      </c>
-      <c r="B308" t="n">
-        <v>11</v>
       </c>
       <c r="C308" t="n">
         <v>100</v>
@@ -19936,10 +19936,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
+        <v>11</v>
+      </c>
+      <c r="B309" t="n">
         <v>55</v>
-      </c>
-      <c r="B309" t="n">
-        <v>11</v>
       </c>
       <c r="C309" t="n">
         <v>35</v>
@@ -20000,10 +20000,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
+        <v>11</v>
+      </c>
+      <c r="B310" t="n">
         <v>61</v>
-      </c>
-      <c r="B310" t="n">
-        <v>11</v>
       </c>
       <c r="C310" t="n">
         <v>92</v>
@@ -20064,10 +20064,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
+        <v>11</v>
+      </c>
+      <c r="B311" t="n">
         <v>66</v>
-      </c>
-      <c r="B311" t="n">
-        <v>11</v>
       </c>
       <c r="C311" t="n">
         <v>80</v>
@@ -20128,10 +20128,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
+        <v>11</v>
+      </c>
+      <c r="B312" t="n">
         <v>71</v>
-      </c>
-      <c r="B312" t="n">
-        <v>11</v>
       </c>
       <c r="C312" t="n">
         <v>76</v>
@@ -20192,10 +20192,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
+        <v>11</v>
+      </c>
+      <c r="B313" t="n">
         <v>75</v>
-      </c>
-      <c r="B313" t="n">
-        <v>11</v>
       </c>
       <c r="C313" t="n">
         <v>7</v>
@@ -20256,10 +20256,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
+        <v>11</v>
+      </c>
+      <c r="B314" t="n">
         <v>84</v>
-      </c>
-      <c r="B314" t="n">
-        <v>11</v>
       </c>
       <c r="C314" t="n">
         <v>42</v>
@@ -20320,10 +20320,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
+        <v>11</v>
+      </c>
+      <c r="B315" t="n">
         <v>87</v>
-      </c>
-      <c r="B315" t="n">
-        <v>11</v>
       </c>
       <c r="C315" t="n">
         <v>57</v>
@@ -20384,10 +20384,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
+        <v>12</v>
+      </c>
+      <c r="B316" t="n">
         <v>3</v>
-      </c>
-      <c r="B316" t="n">
-        <v>12</v>
       </c>
       <c r="C316" t="n">
         <v>51</v>
@@ -20448,10 +20448,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
+        <v>12</v>
+      </c>
+      <c r="B317" t="n">
         <v>4</v>
-      </c>
-      <c r="B317" t="n">
-        <v>12</v>
       </c>
       <c r="C317" t="n">
         <v>93</v>
@@ -20512,10 +20512,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
+        <v>12</v>
+      </c>
+      <c r="B318" t="n">
         <v>5</v>
-      </c>
-      <c r="B318" t="n">
-        <v>12</v>
       </c>
       <c r="C318" t="n">
         <v>82</v>
@@ -20576,10 +20576,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
+        <v>12</v>
+      </c>
+      <c r="B319" t="n">
         <v>8</v>
-      </c>
-      <c r="B319" t="n">
-        <v>12</v>
       </c>
       <c r="C319" t="n">
         <v>38</v>
@@ -20640,10 +20640,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
+        <v>12</v>
+      </c>
+      <c r="B320" t="n">
         <v>9</v>
-      </c>
-      <c r="B320" t="n">
-        <v>12</v>
       </c>
       <c r="C320" t="n">
         <v>13</v>
@@ -20704,10 +20704,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
+        <v>12</v>
+      </c>
+      <c r="B321" t="n">
         <v>10</v>
-      </c>
-      <c r="B321" t="n">
-        <v>12</v>
       </c>
       <c r="C321" t="n">
         <v>1</v>
@@ -20768,10 +20768,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
+        <v>12</v>
+      </c>
+      <c r="B322" t="n">
         <v>13</v>
-      </c>
-      <c r="B322" t="n">
-        <v>12</v>
       </c>
       <c r="C322" t="n">
         <v>71</v>
@@ -20832,10 +20832,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
+        <v>12</v>
+      </c>
+      <c r="B323" t="n">
         <v>16</v>
-      </c>
-      <c r="B323" t="n">
-        <v>12</v>
       </c>
       <c r="C323" t="n">
         <v>2</v>
@@ -20896,10 +20896,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
+        <v>12</v>
+      </c>
+      <c r="B324" t="n">
         <v>17</v>
-      </c>
-      <c r="B324" t="n">
-        <v>12</v>
       </c>
       <c r="C324" t="n">
         <v>2</v>
@@ -20960,10 +20960,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
+        <v>12</v>
+      </c>
+      <c r="B325" t="n">
         <v>18</v>
-      </c>
-      <c r="B325" t="n">
-        <v>12</v>
       </c>
       <c r="C325" t="n">
         <v>93</v>
@@ -21024,10 +21024,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
+        <v>12</v>
+      </c>
+      <c r="B326" t="n">
         <v>19</v>
-      </c>
-      <c r="B326" t="n">
-        <v>12</v>
       </c>
       <c r="C326" t="n">
         <v>88</v>
@@ -21088,10 +21088,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
+        <v>12</v>
+      </c>
+      <c r="B327" t="n">
         <v>21</v>
-      </c>
-      <c r="B327" t="n">
-        <v>12</v>
       </c>
       <c r="C327" t="n">
         <v>18</v>
@@ -21140,10 +21140,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
+        <v>12</v>
+      </c>
+      <c r="B328" t="n">
         <v>26</v>
-      </c>
-      <c r="B328" t="n">
-        <v>12</v>
       </c>
       <c r="C328" t="n">
         <v>4</v>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
+        <v>12</v>
+      </c>
+      <c r="B329" t="n">
         <v>35</v>
-      </c>
-      <c r="B329" t="n">
-        <v>12</v>
       </c>
       <c r="C329" t="n">
         <v>92</v>
@@ -21256,10 +21256,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
+        <v>12</v>
+      </c>
+      <c r="B330" t="n">
         <v>36</v>
-      </c>
-      <c r="B330" t="n">
-        <v>12</v>
       </c>
       <c r="C330" t="n">
         <v>77</v>
@@ -21320,10 +21320,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
+        <v>12</v>
+      </c>
+      <c r="B331" t="n">
         <v>41</v>
-      </c>
-      <c r="B331" t="n">
-        <v>12</v>
       </c>
       <c r="C331" t="n">
         <v>74</v>
@@ -21384,10 +21384,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
+        <v>12</v>
+      </c>
+      <c r="B332" t="n">
         <v>43</v>
-      </c>
-      <c r="B332" t="n">
-        <v>12</v>
       </c>
       <c r="C332" t="n">
         <v>100</v>
@@ -21448,10 +21448,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
+        <v>12</v>
+      </c>
+      <c r="B333" t="n">
         <v>45</v>
-      </c>
-      <c r="B333" t="n">
-        <v>12</v>
       </c>
       <c r="C333" t="n">
         <v>71</v>
@@ -21512,10 +21512,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
+        <v>12</v>
+      </c>
+      <c r="B334" t="n">
         <v>47</v>
-      </c>
-      <c r="B334" t="n">
-        <v>12</v>
       </c>
       <c r="C334" t="n">
         <v>63</v>
@@ -21576,10 +21576,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
+        <v>12</v>
+      </c>
+      <c r="B335" t="n">
         <v>48</v>
-      </c>
-      <c r="B335" t="n">
-        <v>12</v>
       </c>
       <c r="C335" t="n">
         <v>100</v>
@@ -21640,10 +21640,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
+        <v>13</v>
+      </c>
+      <c r="B336" t="n">
         <v>1</v>
-      </c>
-      <c r="B336" t="n">
-        <v>13</v>
       </c>
       <c r="C336" t="n">
         <v>18</v>
@@ -21704,10 +21704,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
+        <v>13</v>
+      </c>
+      <c r="B337" t="n">
         <v>4</v>
-      </c>
-      <c r="B337" t="n">
-        <v>13</v>
       </c>
       <c r="C337" t="n">
         <v>73</v>
@@ -21768,10 +21768,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
+        <v>13</v>
+      </c>
+      <c r="B338" t="n">
         <v>7</v>
-      </c>
-      <c r="B338" t="n">
-        <v>13</v>
       </c>
       <c r="C338" t="n">
         <v>2</v>
@@ -21832,10 +21832,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
+        <v>13</v>
+      </c>
+      <c r="B339" t="n">
         <v>10</v>
-      </c>
-      <c r="B339" t="n">
-        <v>13</v>
       </c>
       <c r="C339" t="n">
         <v>76</v>
@@ -21896,10 +21896,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
+        <v>13</v>
+      </c>
+      <c r="B340" t="n">
         <v>11</v>
-      </c>
-      <c r="B340" t="n">
-        <v>13</v>
       </c>
       <c r="C340" t="n">
         <v>20</v>
@@ -21960,10 +21960,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
+        <v>13</v>
+      </c>
+      <c r="B341" t="n">
         <v>14</v>
-      </c>
-      <c r="B341" t="n">
-        <v>13</v>
       </c>
       <c r="C341" t="n">
         <v>100</v>
@@ -22024,10 +22024,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
+        <v>13</v>
+      </c>
+      <c r="B342" t="n">
         <v>20</v>
-      </c>
-      <c r="B342" t="n">
-        <v>13</v>
       </c>
       <c r="C342" t="n">
         <v>100</v>
@@ -22088,10 +22088,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
+        <v>13</v>
+      </c>
+      <c r="B343" t="n">
         <v>22</v>
-      </c>
-      <c r="B343" t="n">
-        <v>13</v>
       </c>
       <c r="C343" t="n">
         <v>22</v>
@@ -22152,10 +22152,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
+        <v>13</v>
+      </c>
+      <c r="B344" t="n">
         <v>23</v>
-      </c>
-      <c r="B344" t="n">
-        <v>13</v>
       </c>
       <c r="C344" t="n">
         <v>92</v>
@@ -22216,10 +22216,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
+        <v>13</v>
+      </c>
+      <c r="B345" t="n">
         <v>28</v>
-      </c>
-      <c r="B345" t="n">
-        <v>13</v>
       </c>
       <c r="C345" t="n">
         <v>45</v>
@@ -22280,10 +22280,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
+        <v>13</v>
+      </c>
+      <c r="B346" t="n">
         <v>34</v>
-      </c>
-      <c r="B346" t="n">
-        <v>13</v>
       </c>
       <c r="C346" t="n">
         <v>93</v>
@@ -22344,10 +22344,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
+        <v>13</v>
+      </c>
+      <c r="B347" t="n">
         <v>35</v>
-      </c>
-      <c r="B347" t="n">
-        <v>13</v>
       </c>
       <c r="C347" t="n">
         <v>97</v>
@@ -22408,10 +22408,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
+        <v>13</v>
+      </c>
+      <c r="B348" t="n">
         <v>47</v>
-      </c>
-      <c r="B348" t="n">
-        <v>13</v>
       </c>
       <c r="C348" t="n">
         <v>9</v>
@@ -22472,10 +22472,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
+        <v>13</v>
+      </c>
+      <c r="B349" t="n">
         <v>48</v>
-      </c>
-      <c r="B349" t="n">
-        <v>13</v>
       </c>
       <c r="C349" t="n">
         <v>76</v>
@@ -22536,10 +22536,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
+        <v>13</v>
+      </c>
+      <c r="B350" t="n">
         <v>49</v>
-      </c>
-      <c r="B350" t="n">
-        <v>13</v>
       </c>
       <c r="C350" t="n">
         <v>93</v>
@@ -22600,10 +22600,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
+        <v>13</v>
+      </c>
+      <c r="B351" t="n">
         <v>58</v>
-      </c>
-      <c r="B351" t="n">
-        <v>13</v>
       </c>
       <c r="C351" t="n">
         <v>55</v>
@@ -22664,10 +22664,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
+        <v>13</v>
+      </c>
+      <c r="B352" t="n">
         <v>59</v>
-      </c>
-      <c r="B352" t="n">
-        <v>13</v>
       </c>
       <c r="C352" t="n">
         <v>2</v>
@@ -22728,10 +22728,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
+        <v>13</v>
+      </c>
+      <c r="B353" t="n">
         <v>61</v>
-      </c>
-      <c r="B353" t="n">
-        <v>13</v>
       </c>
       <c r="C353" t="n">
         <v>100</v>
@@ -22792,10 +22792,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
+        <v>13</v>
+      </c>
+      <c r="B354" t="n">
         <v>67</v>
-      </c>
-      <c r="B354" t="n">
-        <v>13</v>
       </c>
       <c r="C354" t="n">
         <v>93</v>
@@ -22856,10 +22856,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
+        <v>13</v>
+      </c>
+      <c r="B355" t="n">
         <v>72</v>
-      </c>
-      <c r="B355" t="n">
-        <v>13</v>
       </c>
       <c r="C355" t="n">
         <v>57</v>
@@ -22920,10 +22920,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
+        <v>14</v>
+      </c>
+      <c r="B356" t="n">
         <v>10</v>
-      </c>
-      <c r="B356" t="n">
-        <v>14</v>
       </c>
       <c r="C356" t="n">
         <v>53</v>
@@ -23048,10 +23048,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
+        <v>14</v>
+      </c>
+      <c r="B358" t="n">
         <v>17</v>
-      </c>
-      <c r="B358" t="n">
-        <v>14</v>
       </c>
       <c r="C358" t="n">
         <v>97</v>
@@ -23112,10 +23112,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
+        <v>14</v>
+      </c>
+      <c r="B359" t="n">
         <v>20</v>
-      </c>
-      <c r="B359" t="n">
-        <v>14</v>
       </c>
       <c r="C359" t="n">
         <v>90</v>
@@ -23176,10 +23176,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
+        <v>14</v>
+      </c>
+      <c r="B360" t="n">
         <v>22</v>
-      </c>
-      <c r="B360" t="n">
-        <v>14</v>
       </c>
       <c r="C360" t="n">
         <v>90</v>
@@ -23240,10 +23240,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
+        <v>14</v>
+      </c>
+      <c r="B361" t="n">
         <v>24</v>
-      </c>
-      <c r="B361" t="n">
-        <v>14</v>
       </c>
       <c r="C361" t="n">
         <v>38</v>
@@ -23304,10 +23304,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
+        <v>14</v>
+      </c>
+      <c r="B362" t="n">
         <v>32</v>
-      </c>
-      <c r="B362" t="n">
-        <v>14</v>
       </c>
       <c r="C362" t="n">
         <v>53</v>
@@ -23368,10 +23368,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
+        <v>14</v>
+      </c>
+      <c r="B363" t="n">
         <v>34</v>
-      </c>
-      <c r="B363" t="n">
-        <v>14</v>
       </c>
       <c r="C363" t="n">
         <v>90</v>
@@ -23432,10 +23432,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
+        <v>14</v>
+      </c>
+      <c r="B364" t="n">
         <v>37</v>
-      </c>
-      <c r="B364" t="n">
-        <v>14</v>
       </c>
       <c r="C364" t="n">
         <v>55</v>
@@ -23496,10 +23496,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
+        <v>14</v>
+      </c>
+      <c r="B365" t="n">
         <v>45</v>
-      </c>
-      <c r="B365" t="n">
-        <v>14</v>
       </c>
       <c r="C365" t="n">
         <v>53</v>
@@ -23560,10 +23560,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
+        <v>14</v>
+      </c>
+      <c r="B366" t="n">
         <v>58</v>
-      </c>
-      <c r="B366" t="n">
-        <v>14</v>
       </c>
       <c r="C366" t="n">
         <v>53</v>
@@ -23624,10 +23624,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
+        <v>14</v>
+      </c>
+      <c r="B367" t="n">
         <v>61</v>
-      </c>
-      <c r="B367" t="n">
-        <v>14</v>
       </c>
       <c r="C367" t="n">
         <v>53</v>
@@ -23688,10 +23688,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
+        <v>14</v>
+      </c>
+      <c r="B368" t="n">
         <v>63</v>
-      </c>
-      <c r="B368" t="n">
-        <v>14</v>
       </c>
       <c r="C368" t="n">
         <v>92</v>
@@ -23752,10 +23752,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
+        <v>14</v>
+      </c>
+      <c r="B369" t="n">
         <v>69</v>
-      </c>
-      <c r="B369" t="n">
-        <v>14</v>
       </c>
       <c r="C369" t="n">
         <v>16</v>
@@ -23816,10 +23816,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
+        <v>14</v>
+      </c>
+      <c r="B370" t="n">
         <v>72</v>
-      </c>
-      <c r="B370" t="n">
-        <v>14</v>
       </c>
       <c r="C370" t="n">
         <v>53</v>
@@ -23880,10 +23880,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
+        <v>14</v>
+      </c>
+      <c r="B371" t="n">
         <v>85</v>
-      </c>
-      <c r="B371" t="n">
-        <v>14</v>
       </c>
       <c r="C371" t="n">
         <v>79</v>
@@ -23944,10 +23944,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
+        <v>14</v>
+      </c>
+      <c r="B372" t="n">
         <v>92</v>
-      </c>
-      <c r="B372" t="n">
-        <v>14</v>
       </c>
       <c r="C372" t="n">
         <v>66</v>
@@ -24000,10 +24000,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
+        <v>14</v>
+      </c>
+      <c r="B373" t="n">
         <v>93</v>
-      </c>
-      <c r="B373" t="n">
-        <v>14</v>
       </c>
       <c r="C373" t="n">
         <v>51</v>
@@ -24064,10 +24064,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
+        <v>14</v>
+      </c>
+      <c r="B374" t="n">
         <v>94</v>
-      </c>
-      <c r="B374" t="n">
-        <v>14</v>
       </c>
       <c r="C374" t="n">
         <v>38</v>
@@ -24128,10 +24128,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
+        <v>14</v>
+      </c>
+      <c r="B375" t="n">
         <v>95</v>
-      </c>
-      <c r="B375" t="n">
-        <v>14</v>
       </c>
       <c r="C375" t="n">
         <v>11</v>
@@ -24192,10 +24192,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
+        <v>14</v>
+      </c>
+      <c r="B376" t="n">
         <v>97</v>
-      </c>
-      <c r="B376" t="n">
-        <v>14</v>
       </c>
       <c r="C376" t="n">
         <v>94</v>
@@ -24256,10 +24256,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
+        <v>14</v>
+      </c>
+      <c r="B377" t="n">
         <v>101</v>
-      </c>
-      <c r="B377" t="n">
-        <v>14</v>
       </c>
       <c r="C377" t="n">
         <v>55</v>
@@ -24316,10 +24316,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
+        <v>14</v>
+      </c>
+      <c r="B378" t="n">
         <v>102</v>
-      </c>
-      <c r="B378" t="n">
-        <v>14</v>
       </c>
       <c r="C378" t="n">
         <v>78</v>
@@ -24380,10 +24380,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
+        <v>15</v>
+      </c>
+      <c r="B379" t="n">
         <v>3</v>
-      </c>
-      <c r="B379" t="n">
-        <v>15</v>
       </c>
       <c r="C379" t="n">
         <v>35</v>
@@ -24444,10 +24444,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
+        <v>15</v>
+      </c>
+      <c r="B380" t="n">
         <v>6</v>
-      </c>
-      <c r="B380" t="n">
-        <v>15</v>
       </c>
       <c r="C380" t="n">
         <v>93</v>
@@ -24508,10 +24508,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
+        <v>15</v>
+      </c>
+      <c r="B381" t="n">
         <v>11</v>
-      </c>
-      <c r="B381" t="n">
-        <v>15</v>
       </c>
       <c r="C381" t="n">
         <v>73</v>
@@ -24572,10 +24572,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
+        <v>15</v>
+      </c>
+      <c r="B382" t="n">
         <v>17</v>
-      </c>
-      <c r="B382" t="n">
-        <v>15</v>
       </c>
       <c r="C382" t="n">
         <v>55</v>
@@ -24636,10 +24636,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
+        <v>15</v>
+      </c>
+      <c r="B383" t="n">
         <v>20</v>
-      </c>
-      <c r="B383" t="n">
-        <v>15</v>
       </c>
       <c r="C383" t="n">
         <v>93</v>
@@ -24700,10 +24700,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
+        <v>15</v>
+      </c>
+      <c r="B384" t="n">
         <v>29</v>
-      </c>
-      <c r="B384" t="n">
-        <v>15</v>
       </c>
       <c r="C384" t="n">
         <v>18</v>
@@ -24764,10 +24764,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
+        <v>15</v>
+      </c>
+      <c r="B385" t="n">
         <v>33</v>
-      </c>
-      <c r="B385" t="n">
-        <v>15</v>
       </c>
       <c r="C385" t="n">
         <v>91</v>
@@ -24828,10 +24828,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
+        <v>15</v>
+      </c>
+      <c r="B386" t="n">
         <v>34</v>
-      </c>
-      <c r="B386" t="n">
-        <v>15</v>
       </c>
       <c r="C386" t="n">
         <v>93</v>
@@ -24892,10 +24892,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
+        <v>15</v>
+      </c>
+      <c r="B387" t="n">
         <v>35</v>
-      </c>
-      <c r="B387" t="n">
-        <v>15</v>
       </c>
       <c r="C387" t="n">
         <v>90</v>
@@ -24956,10 +24956,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
+        <v>15</v>
+      </c>
+      <c r="B388" t="n">
         <v>36</v>
-      </c>
-      <c r="B388" t="n">
-        <v>15</v>
       </c>
       <c r="C388" t="n">
         <v>57</v>
@@ -25020,10 +25020,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
+        <v>15</v>
+      </c>
+      <c r="B389" t="n">
         <v>37</v>
-      </c>
-      <c r="B389" t="n">
-        <v>15</v>
       </c>
       <c r="C389" t="n">
         <v>18</v>
@@ -25084,10 +25084,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
+        <v>15</v>
+      </c>
+      <c r="B390" t="n">
         <v>48</v>
-      </c>
-      <c r="B390" t="n">
-        <v>15</v>
       </c>
       <c r="C390" t="n">
         <v>90</v>
@@ -25148,10 +25148,10 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
+        <v>15</v>
+      </c>
+      <c r="B391" t="n">
         <v>50</v>
-      </c>
-      <c r="B391" t="n">
-        <v>15</v>
       </c>
       <c r="C391" t="n">
         <v>1</v>
@@ -25212,10 +25212,10 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
+        <v>15</v>
+      </c>
+      <c r="B392" t="n">
         <v>55</v>
-      </c>
-      <c r="B392" t="n">
-        <v>15</v>
       </c>
       <c r="C392" t="n">
         <v>92</v>
@@ -25276,10 +25276,10 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
+        <v>15</v>
+      </c>
+      <c r="B393" t="n">
         <v>56</v>
-      </c>
-      <c r="B393" t="n">
-        <v>15</v>
       </c>
       <c r="C393" t="n">
         <v>13</v>
@@ -25340,10 +25340,10 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
+        <v>15</v>
+      </c>
+      <c r="B394" t="n">
         <v>58</v>
-      </c>
-      <c r="B394" t="n">
-        <v>15</v>
       </c>
       <c r="C394" t="n">
         <v>55</v>
@@ -25392,10 +25392,10 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
+        <v>15</v>
+      </c>
+      <c r="B395" t="n">
         <v>59</v>
-      </c>
-      <c r="B395" t="n">
-        <v>15</v>
       </c>
       <c r="C395" t="n">
         <v>15</v>
@@ -25456,10 +25456,10 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
+        <v>15</v>
+      </c>
+      <c r="B396" t="n">
         <v>62</v>
-      </c>
-      <c r="B396" t="n">
-        <v>15</v>
       </c>
       <c r="C396" t="n">
         <v>57</v>
@@ -25520,10 +25520,10 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
+        <v>15</v>
+      </c>
+      <c r="B397" t="n">
         <v>64</v>
-      </c>
-      <c r="B397" t="n">
-        <v>15</v>
       </c>
       <c r="C397" t="n">
         <v>93</v>
@@ -25584,10 +25584,10 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
+        <v>15</v>
+      </c>
+      <c r="B398" t="n">
         <v>65</v>
-      </c>
-      <c r="B398" t="n">
-        <v>15</v>
       </c>
       <c r="C398" t="n">
         <v>18</v>
@@ -25648,10 +25648,10 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
+        <v>15</v>
+      </c>
+      <c r="B399" t="n">
         <v>74</v>
-      </c>
-      <c r="B399" t="n">
-        <v>15</v>
       </c>
       <c r="C399" t="n">
         <v>55</v>
@@ -25712,10 +25712,10 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
+        <v>15</v>
+      </c>
+      <c r="B400" t="n">
         <v>76</v>
-      </c>
-      <c r="B400" t="n">
-        <v>15</v>
       </c>
       <c r="C400" t="n">
         <v>91</v>
@@ -25776,10 +25776,10 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
+        <v>15</v>
+      </c>
+      <c r="B401" t="n">
         <v>78</v>
-      </c>
-      <c r="B401" t="n">
-        <v>15</v>
       </c>
       <c r="C401" t="n">
         <v>6</v>
